--- a/AAII_Financials/Yearly/WABC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WABC_YR_FIN.xlsx
@@ -2216,7 +2216,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>610800</v>
+        <v>611300</v>
       </c>
       <c r="E46" s="3">
         <v>651800</v>
@@ -2471,7 +2471,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4318800</v>
+        <v>4318400</v>
       </c>
       <c r="E47" s="3">
         <v>4269200</v>
